--- a/aceros.xlsx
+++ b/aceros.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57314\Desktop\Nueva carpeta\Thesis Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66a0e04faeb60c1/Escritorio/Thesis-project-USCO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D722CD93-E143-45A3-BC59-F20874E1AD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{D722CD93-E143-45A3-BC59-F20874E1AD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE503DA-8E9E-425F-933D-83017576D193}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -107,6 +107,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>257176</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>452106</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921DC3A4-B787-E1A3-A683-18EAFCC4BD23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="866776" y="1257300"/>
+          <a:ext cx="4157330" cy="2628900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -427,5 +476,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>